--- a/Pravartiya/data/Searching_agent_output.xlsx
+++ b/Pravartiya/data/Searching_agent_output.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>Verticals</t>
   </si>
@@ -52,24 +52,21 @@
     <t>April</t>
   </si>
   <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>Securities and Exchange Board of India (Real Estate Investment Trusts) (Amendment) Regulations, 2026</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1776658226643.pdf</t>
-  </si>
-  <si>
-    <t>Securities_and_Exchange_Board_of_India_Real_Estate_Investment_Trusts_Amendment_R_69349c5e.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/April/Securities_and_Exchange_Board_of_India_Real_Estate_Investment_Trusts_Amendment_R_69349c5e.pdf</t>
-  </si>
-  <si>
     <t>2026-04-16</t>
   </si>
   <si>
+    <t>Securities and Exchange Board of India (Intermediaries) Regulations, 2008 [Last amended on April 16, 2026]</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1777024110709.pdf</t>
+  </si>
+  <si>
+    <t>Securities_and_Exchange_Board_of_India_Intermediaries_Regulations_2008_Last_amen_54e7cd38.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/April/Securities_and_Exchange_Board_of_India_Intermediaries_Regulations_2008_Last_amen_54e7cd38.pdf</t>
+  </si>
+  <si>
     <t>Securities and Exchange Board of India (Intermediaries) (Amendment) Regulations, 2026</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
   </si>
   <si>
     <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/April/Securities_and_Exchange_Board_of_India_Intermediaries_Amendment_Regulations_2026_1c146097.pdf</t>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
@@ -90,7 +84,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,6 +96,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -155,30 +155,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -491,11 +494,11 @@
   <cols>
     <col min="1" max="1" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="8" width="114.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
@@ -507,7 +510,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -530,251 +533,139 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="4">
         <v>2026</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="4">
         <v>2026</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
-      <c r="A4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
-      <c r="A5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
-      <c r="A6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
-      <c r="A7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
-      <c r="A8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Pravartiya/data/Searching_agent_output.xlsx
+++ b/Pravartiya/data/Searching_agent_output.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="22">
   <si>
     <t>Verticals</t>
   </si>
@@ -49,34 +49,37 @@
     <t>Regulations</t>
   </si>
   <si>
-    <t>April</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>Securities and Exchange Board of India (Intermediaries) Regulations, 2008 [Last amended on April 16, 2026]</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1777024110709.pdf</t>
-  </si>
-  <si>
-    <t>Securities_and_Exchange_Board_of_India_Intermediaries_Regulations_2008_Last_amen_54e7cd38.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/April/Securities_and_Exchange_Board_of_India_Intermediaries_Regulations_2008_Last_amen_54e7cd38.pdf</t>
-  </si>
-  <si>
-    <t>Securities and Exchange Board of India (Intermediaries) (Amendment) Regulations, 2026</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1776419077625.pdf</t>
-  </si>
-  <si>
-    <t>Securities_and_Exchange_Board_of_India_Intermediaries_Amendment_Regulations_2026_1c146097.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/April/Securities_and_Exchange_Board_of_India_Intermediaries_Amendment_Regulations_2026_1c146097.pdf</t>
+    <t>January</t>
+  </si>
+  <si>
+    <t>2026-01-22</t>
+  </si>
+  <si>
+    <t>Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) Regulations, 2015 [Last amended on January 22, 2026]</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1777351317428.pdf</t>
+  </si>
+  <si>
+    <t>Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_500e67fd.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/January/Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_500e67fd.pdf</t>
+  </si>
+  <si>
+    <t>Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) (Amendment) Regulations, 2026</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jan-2026/1769600297568.pdf</t>
+  </si>
+  <si>
+    <t>Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_d9dfa16a.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/January/Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_d9dfa16a.pdf</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -101,7 +104,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -155,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -172,8 +175,14 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -182,7 +191,7 @@
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -492,15 +501,15 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="114.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="114.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -532,7 +541,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -561,7 +570,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -590,80 +599,176 @@
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="A9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
-      <c r="C10" s="6"/>
+      <c r="C10" s="4"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="7"/>
+      <c r="G10" s="9"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>

--- a/Pravartiya/data/Searching_agent_output.xlsx
+++ b/Pravartiya/data/Searching_agent_output.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>Verticals</t>
   </si>
@@ -52,34 +52,31 @@
     <t>January</t>
   </si>
   <si>
-    <t>2026-01-22</t>
-  </si>
-  <si>
-    <t>Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) Regulations, 2015 [Last amended on January 22, 2026]</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1777351317428.pdf</t>
-  </si>
-  <si>
-    <t>Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_500e67fd.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/January/Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_500e67fd.pdf</t>
-  </si>
-  <si>
-    <t>Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) (Amendment) Regulations, 2026</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jan-2026/1769600297568.pdf</t>
-  </si>
-  <si>
-    <t>Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_d9dfa16a.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/January/Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_d9dfa16a.pdf</t>
-  </si>
-  <si>
-    <t/>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>Securities and Exchange Board of India (Credit Rating Agencies) Regulations, 1999 [Last amended on January 15, 2026]</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jan-2026/1768814495033.pdf</t>
+  </si>
+  <si>
+    <t>Securities_and_Exchange_Board_of_India_Credit_Rating_Agencies_Regulations_1999_L_762cf976.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/January/Securities_and_Exchange_Board_of_India_Credit_Rating_Agencies_Regulations_1999_L_762cf976.pdf</t>
+  </si>
+  <si>
+    <t>Securities and Exchange Board of India (Credit Rating Agencies) (Amendment) Regulations, 2026</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jan-2026/1768814277525.pdf</t>
+  </si>
+  <si>
+    <t>Securities_and_Exchange_Board_of_India_Credit_Rating_Agencies_Amendment_Regulati_92ea8cea.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/January/Securities_and_Exchange_Board_of_India_Credit_Rating_Agencies_Amendment_Regulati_92ea8cea.pdf</t>
   </si>
 </sst>
 </file>
@@ -158,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -173,15 +170,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
@@ -501,15 +489,15 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="10" width="114.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="114.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -600,166 +588,70 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
       <c r="C8" s="4"/>
-      <c r="D8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3"/>
@@ -768,7 +660,7 @@
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="9"/>
+      <c r="G10" s="6"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>

--- a/Pravartiya/data/Searching_agent_output.xlsx
+++ b/Pravartiya/data/Searching_agent_output.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Verticals</t>
   </si>
@@ -43,40 +43,28 @@
     <t>Path</t>
   </si>
   <si>
-    <t>SEBI</t>
-  </si>
-  <si>
-    <t>Regulations</t>
-  </si>
-  <si>
-    <t>January</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>Securities and Exchange Board of India (Credit Rating Agencies) Regulations, 1999 [Last amended on January 15, 2026]</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jan-2026/1768814495033.pdf</t>
-  </si>
-  <si>
-    <t>Securities_and_Exchange_Board_of_India_Credit_Rating_Agencies_Regulations_1999_L_762cf976.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/January/Securities_and_Exchange_Board_of_India_Credit_Rating_Agencies_Regulations_1999_L_762cf976.pdf</t>
-  </si>
-  <si>
-    <t>Securities and Exchange Board of India (Credit Rating Agencies) (Amendment) Regulations, 2026</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jan-2026/1768814277525.pdf</t>
-  </si>
-  <si>
-    <t>Securities_and_Exchange_Board_of_India_Credit_Rating_Agencies_Amendment_Regulati_92ea8cea.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/January/Securities_and_Exchange_Board_of_India_Credit_Rating_Agencies_Amendment_Regulati_92ea8cea.pdf</t>
+    <t>Listed Companies</t>
+  </si>
+  <si>
+    <t>Circular-BSE</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>Update on single filing system through API-based integration between Stock Exchanges</t>
+  </si>
+  <si>
+    <t>https://www.bseindia.com/markets/MarketInfo/DispNewNoticesCirculars?page=20260220-44</t>
+  </si>
+  <si>
+    <t>Update_on_single_filing_system_through_API_based_integration_between_Stock_Excha_40202074.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-BSE/2026/February/Update_on_single_filing_system_through_API_based_integration_between_Stock_Excha_40202074.pdf</t>
   </si>
 </sst>
 </file>
@@ -84,7 +72,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,6 +97,12 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -169,17 +163,17 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -486,7 +480,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -494,7 +488,7 @@
     <col min="3" max="3" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="114.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="82.7192857142857" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -559,33 +553,15 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3"/>
@@ -601,7 +577,7 @@
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -612,7 +588,7 @@
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
+      <c r="C6" s="6"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -623,7 +599,7 @@
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
+      <c r="C7" s="6"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -631,39 +607,6 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
